--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1372,6 +1372,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7260,7 +7264,7 @@
         <v>434</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>435</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7269,10 +7273,10 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7283,10 +7287,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7312,10 +7316,10 @@
         <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7366,7 +7370,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7378,7 +7382,7 @@
         <v>434</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>435</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7387,10 +7391,10 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -7401,10 +7405,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7430,16 +7434,16 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7467,10 +7471,10 @@
         <v>117</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7488,7 +7492,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7506,10 +7510,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>368</v>
@@ -7523,10 +7527,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7552,16 +7556,16 @@
         <v>182</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7589,10 +7593,10 @@
         <v>269</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7610,7 +7614,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7628,10 +7632,10 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>368</v>
@@ -7645,10 +7649,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7671,17 +7675,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7730,7 +7734,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7754,7 +7758,7 @@
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7765,10 +7769,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,10 +7798,10 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7848,7 +7852,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7869,10 +7873,10 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7883,10 +7887,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7909,16 +7913,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7968,7 +7972,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7989,10 +7993,10 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8003,10 +8007,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8029,16 +8033,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8088,7 +8092,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8109,10 +8113,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8123,10 +8127,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8152,16 +8156,16 @@
         <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8210,7 +8214,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8231,10 +8235,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8245,10 +8249,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8363,10 +8367,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8483,10 +8487,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8605,10 +8609,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8634,13 +8638,13 @@
         <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>268</v>
@@ -8692,7 +8696,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -8710,7 +8714,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>274</v>
@@ -8727,10 +8731,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8756,13 +8760,13 @@
         <v>339</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>341</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>343</v>
@@ -8814,7 +8818,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8832,7 +8836,7 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>346</v>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8878,13 +8882,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>353</v>
@@ -8936,7 +8940,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8971,10 +8975,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9058,7 +9062,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9093,10 +9097,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9122,10 +9126,10 @@
         <v>83</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>418</v>
@@ -9180,7 +9184,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
